--- a/extended_model/data/parameters.xlsx
+++ b/extended_model/data/parameters.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCALAR_PARAMS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEMAND" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUPPLIER_CAP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FACTORY_CAP" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MODE_CAP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_THROUGHPUT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_STORAGE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_INVEST" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_OPCOST" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_SWITCH" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOLD_COST" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BACK_COST" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FACTORY_DC_COST" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_CUST_COST" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SCALAR_PARAMS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DEMAND" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SUPPLIER_CAP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FACTORY_CAP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MODE_CAP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DC_THROUGHPUT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DC_STORAGE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DC_INVEST" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DC_OPCOST" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="DC_SWITCH" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="HOLD_COST" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="BACK_COST" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="FACTORY_DC_COST" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="DC_CUST_COST" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -516,6 +516,16 @@
       </c>
       <c r="B4" s="2" t="n">
         <v>3600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eta</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
